--- a/Data/Building/TeaRoom.WaterDispenser001.xlsx
+++ b/Data/Building/TeaRoom.WaterDispenser001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:I304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709276646</v>
+        <v>1711865717</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +533,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709277035</v>
+        <v>1711866181</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +551,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +570,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709277210</v>
+        <v>1711866354</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -569,12 +580,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -595,7 +611,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709277373</v>
+        <v>1711866752</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -605,7 +621,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -613,6 +629,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +648,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709277638</v>
+        <v>1711867444</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -641,12 +658,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -667,7 +689,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709277748</v>
+        <v>1711867872</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -677,7 +699,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -685,6 +707,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +726,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709277794</v>
+        <v>1711868284</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -713,12 +736,17 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -739,7 +767,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709277912</v>
+        <v>1711868671</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +785,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +804,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709277950</v>
+        <v>1711868973</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -785,7 +814,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -793,6 +822,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +841,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709277965</v>
+        <v>1711869085</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -821,12 +851,17 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -847,7 +882,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709278302</v>
+        <v>1711869386</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +900,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +919,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709278887</v>
+        <v>1711869491</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +937,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +956,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709279393</v>
+        <v>1711869851</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +974,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +993,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709266852</v>
+        <v>1711874750</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +1011,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1030,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709267220</v>
+        <v>1711875258</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1048,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1067,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709267241</v>
+        <v>1711945313</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1085,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1104,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709267479</v>
+        <v>1711945665</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1122,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1141,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709267735</v>
+        <v>1711945712</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1109,7 +1151,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1117,6 +1159,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1178,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709268084</v>
+        <v>1711945777</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1196,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1215,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709268361</v>
+        <v>1711945866</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1181,7 +1225,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1189,6 +1233,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1252,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709268652</v>
+        <v>1711946853</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1217,7 +1262,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1225,6 +1270,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1289,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709268724</v>
+        <v>1711947198</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1307,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1326,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709268911</v>
+        <v>1711947391</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1344,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1363,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709270785</v>
+        <v>1711947966</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1381,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1400,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709271185</v>
+        <v>1711948348</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1418,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1437,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709271311</v>
+        <v>1711949645</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1397,12 +1447,17 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1478,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709351724</v>
+        <v>1711950132</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1433,7 +1488,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1441,6 +1496,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1515,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709352082</v>
+        <v>1712032704</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1469,7 +1525,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1477,6 +1533,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1552,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709354523</v>
+        <v>1712032911</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1505,7 +1562,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1513,6 +1570,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1589,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709354769</v>
+        <v>1712033347</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1541,12 +1599,17 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1630,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709354902</v>
+        <v>1712033782</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1648,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1667,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709355323</v>
+        <v>1712034061</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1613,7 +1677,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1621,6 +1685,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1704,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709355805</v>
+        <v>1712034846</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1649,12 +1714,17 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1745,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709356804</v>
+        <v>1712035187</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1685,7 +1755,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1693,6 +1763,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1782,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709357179</v>
+        <v>1712035375</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1721,12 +1792,17 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1823,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709357302</v>
+        <v>1712035713</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1860,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709357331</v>
+        <v>1712036029</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1878,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1901,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709357733</v>
+        <v>1712036446</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1919,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1938,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709358841</v>
+        <v>1712037126</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1956,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1979,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709359280</v>
+        <v>1712037634</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1997,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +2016,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709359378</v>
+        <v>1712037913</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +2034,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2053,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709437344</v>
+        <v>1712120478</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2071,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2094,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709437797</v>
+        <v>1712120841</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2112,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2131,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709439271</v>
+        <v>1712121162</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2149,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2172,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709439638</v>
+        <v>1712121467</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2190,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2209,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709441668</v>
+        <v>1712121640</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2227,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2250,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709441945</v>
+        <v>1712121924</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2268,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2287,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709442002</v>
+        <v>1712122734</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2189,7 +2297,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2197,6 +2305,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2324,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709442114</v>
+        <v>1712123162</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2225,7 +2334,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2233,6 +2342,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2361,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709442380</v>
+        <v>1712123391</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2261,12 +2371,17 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2402,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709443332</v>
+        <v>1712123809</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2297,7 +2412,7 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2305,6 +2420,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2439,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709443658</v>
+        <v>1712124613</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2333,7 +2449,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2341,6 +2457,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2476,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709443823</v>
+        <v>1712125029</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2494,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2513,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709444653</v>
+        <v>1712126206</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2531,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2550,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709445153</v>
+        <v>1712126741</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2568,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2587,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709447221</v>
+        <v>1712127030</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2605,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2624,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709447750</v>
+        <v>1712127482</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2642,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2661,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709526351</v>
+        <v>1712204146</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2679,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2702,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709526767</v>
+        <v>1712204536</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2720,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2739,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709526897</v>
+        <v>1712205382</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2757,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2780,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709527423</v>
+        <v>1712205848</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2798,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2817,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709527613</v>
+        <v>1712206313</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2693,12 +2827,17 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2858,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709528179</v>
+        <v>1712206662</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2729,7 +2868,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2737,6 +2876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2895,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709528430</v>
+        <v>1712207297</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2765,12 +2905,17 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2936,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709528520</v>
+        <v>1712207770</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2973,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709528620</v>
+        <v>1712208060</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2837,12 +2983,17 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -2863,7 +3014,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709529806</v>
+        <v>1712208404</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2873,7 +3024,7 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2881,6 +3032,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +3051,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709530255</v>
+        <v>1712208410</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2909,12 +3061,17 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3092,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709533791</v>
+        <v>1712208822</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2945,7 +3102,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2953,6 +3110,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3129,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709534268</v>
+        <v>1712210919</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2981,12 +3139,17 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3170,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709614464</v>
+        <v>1712211456</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3017,7 +3180,7 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3025,6 +3188,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3207,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709614895</v>
+        <v>1712211573</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3225,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3244,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709616928</v>
+        <v>1712289861</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3262,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3285,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709617227</v>
+        <v>1712290212</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3303,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3322,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709617337</v>
+        <v>1712291091</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3340,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3359,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709617642</v>
+        <v>1712291488</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3377,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3396,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709617745</v>
+        <v>1712291651</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3414,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3437,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709618156</v>
+        <v>1712292123</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3455,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3474,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709618402</v>
+        <v>1712292173</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3492,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3515,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709618812</v>
+        <v>1712292564</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3533,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3552,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709619122</v>
+        <v>1712292797</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3570,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3589,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709619998</v>
+        <v>1712294509</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3607,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3630,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709620460</v>
+        <v>1712295069</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3648,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3667,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709622520</v>
+        <v>1712295109</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3685,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3704,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709622974</v>
+        <v>1712295547</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3722,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3741,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709867726</v>
+        <v>1712295775</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3557,7 +3751,7 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3565,6 +3759,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3778,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709868152</v>
+        <v>1712298821</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3593,12 +3788,17 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3819,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709868730</v>
+        <v>1712299281</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3629,7 +3829,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3637,6 +3837,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3856,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709869029</v>
+        <v>1712552227</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3665,12 +3866,17 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3897,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709869630</v>
+        <v>1712552540</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3701,7 +3907,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3709,6 +3915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3934,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709869985</v>
+        <v>1712552632</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3971,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709870077</v>
+        <v>1712552817</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3989,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +4012,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709870321</v>
+        <v>1712553047</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +4030,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +4049,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709870625</v>
+        <v>1712553160</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +4067,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +4090,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709871053</v>
+        <v>1712553193</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +4108,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4127,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709871416</v>
+        <v>1712553437</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3917,7 +4137,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3925,6 +4145,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4164,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709871793</v>
+        <v>1712553738</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3953,7 +4174,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3961,6 +4182,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4201,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709872877</v>
+        <v>1712554206</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3989,7 +4211,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3997,6 +4219,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4238,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709873266</v>
+        <v>1712554607</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4025,12 +4248,17 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4279,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709873742</v>
+        <v>1712555006</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4061,7 +4289,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4069,6 +4297,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4316,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709874191</v>
+        <v>1712556499</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4097,12 +4326,17 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4357,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709874327</v>
+        <v>1712557009</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4375,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4394,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709953546</v>
+        <v>1712634599</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4412,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4431,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709953917</v>
+        <v>1712634751</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4449,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4468,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709958207</v>
+        <v>1712635815</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4486,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4509,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709958598</v>
+        <v>1712636183</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4527,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4546,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709959821</v>
+        <v>1712638418</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4564,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4583,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709960124</v>
+        <v>1712638746</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4601,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4620,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709960336</v>
+        <v>1712638969</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4638,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4657,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709960533</v>
+        <v>1712639147</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4675,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4698,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709960886</v>
+        <v>1712639495</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4716,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4735,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709960916</v>
+        <v>1712639668</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4753,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4776,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709961184</v>
+        <v>1712640044</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4794,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4813,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709961788</v>
+        <v>1712641331</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4831,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4854,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709962290</v>
+        <v>1712641766</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4872,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4891,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709962942</v>
+        <v>1712642188</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4645,6 +4909,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4932,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709963473</v>
+        <v>1712642665</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4950,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4969,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710045440</v>
+        <v>1712643420</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4987,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +5010,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710045830</v>
+        <v>1712643926</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +5028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +5047,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710046682</v>
+        <v>1712725216</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +5065,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +5088,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710047099</v>
+        <v>1712725655</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +5106,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +5125,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710048179</v>
+        <v>1712726486</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +5143,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5166,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710048502</v>
+        <v>1712726881</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5184,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5203,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710049425</v>
+        <v>1712727024</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4925,7 +5213,7 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4933,6 +5221,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5240,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710049948</v>
+        <v>1712727171</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4961,12 +5250,17 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -4987,7 +5281,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710050833</v>
+        <v>1712727480</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4997,7 +5291,7 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5005,6 +5299,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5023,7 +5318,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710051220</v>
+        <v>1712728137</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5033,12 +5328,17 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5359,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710051460</v>
+        <v>1712728522</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5077,6 +5377,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5396,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710051660</v>
+        <v>1712729714</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5113,6 +5414,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5131,7 +5433,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710052149</v>
+        <v>1712730232</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5149,6 +5451,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5167,7 +5470,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710054573</v>
+        <v>1712730241</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5177,7 +5480,7 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5185,6 +5488,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5203,7 +5507,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710054920</v>
+        <v>1712731493</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5213,7 +5517,7 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5221,6 +5525,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5544,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710131985</v>
+        <v>1712731959</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5249,7 +5554,7 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5257,6 +5562,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5581,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710132407</v>
+        <v>1712808741</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5285,7 +5591,7 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5293,6 +5599,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5618,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710134444</v>
+        <v>1712809136</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5321,7 +5628,7 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5329,6 +5636,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5347,7 +5655,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710134848</v>
+        <v>1712809521</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5357,12 +5665,17 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5696,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710134969</v>
+        <v>1712809816</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5393,7 +5706,7 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5401,6 +5714,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5733,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710135104</v>
+        <v>1712810364</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5429,7 +5743,7 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5437,6 +5751,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5770,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710135230</v>
+        <v>1712810546</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5473,6 +5788,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5491,7 +5807,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710136639</v>
+        <v>1712810735</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5501,7 +5817,7 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5509,6 +5825,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5527,7 +5844,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710136941</v>
+        <v>1712811965</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5537,12 +5854,17 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5885,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710137483</v>
+        <v>1712812436</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5573,7 +5895,7 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5581,6 +5903,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5922,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710137987</v>
+        <v>1712812538</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5609,12 +5932,17 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5963,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710138163</v>
+        <v>1712812807</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5981,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +6000,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710138246</v>
+        <v>1712812908</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5681,7 +6010,7 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5689,6 +6018,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5707,7 +6037,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710138620</v>
+        <v>1712814050</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5717,12 +6047,17 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5743,7 +6078,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710215503</v>
+        <v>1712814499</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5753,7 +6088,7 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5761,6 +6096,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +6115,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710215956</v>
+        <v>1712815256</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5789,12 +6125,17 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5815,7 +6156,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710219517</v>
+        <v>1712815706</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5825,7 +6166,7 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5833,6 +6174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5851,7 +6193,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710219959</v>
+        <v>1712896968</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5861,7 +6203,7 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5869,6 +6211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6230,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710220674</v>
+        <v>1712897498</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5897,7 +6240,7 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5905,6 +6248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5923,7 +6267,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710221181</v>
+        <v>1712897870</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5933,12 +6277,17 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -5959,7 +6308,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710221188</v>
+        <v>1712898229</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5969,7 +6318,7 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5977,6 +6326,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6345,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710221291</v>
+        <v>1712898242</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6363,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6382,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710221473</v>
+        <v>1712899183</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6400,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6423,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710221489</v>
+        <v>1712899571</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6441,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6460,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710221887</v>
+        <v>1712899986</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6113,12 +6470,17 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6501,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710222494</v>
+        <v>1712900331</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6149,7 +6511,7 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6157,6 +6519,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6538,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710222922</v>
+        <v>1712900405</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6556,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6575,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710224769</v>
+        <v>1712900727</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6229,6 +6593,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6247,7 +6612,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710225152</v>
+        <v>1712901089</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6265,6 +6630,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6283,7 +6649,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710226145</v>
+        <v>1712904043</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6301,6 +6667,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6319,7 +6686,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710226673</v>
+        <v>1712904485</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6337,6 +6704,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6355,7 +6723,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710474990</v>
+        <v>1713153272</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6373,6 +6741,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6391,7 +6760,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710475261</v>
+        <v>1713153720</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6409,6 +6778,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6427,7 +6797,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710476266</v>
+        <v>1713154050</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6445,6 +6815,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6463,7 +6838,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710476782</v>
+        <v>1713154480</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6481,6 +6856,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6499,7 +6875,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710477196</v>
+        <v>1713154616</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6517,6 +6893,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6535,7 +6912,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710478915</v>
+        <v>1713155051</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6553,6 +6930,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6571,7 +6949,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710479416</v>
+        <v>1713155521</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6589,6 +6967,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6607,7 +6986,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710479707</v>
+        <v>1713156115</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6625,6 +7004,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6643,7 +7023,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710480193</v>
+        <v>1713156589</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6661,6 +7041,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6679,7 +7060,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710480858</v>
+        <v>1713156960</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6697,6 +7078,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6715,7 +7097,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710481345</v>
+        <v>1713157364</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6733,6 +7115,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6751,7 +7134,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710481371</v>
+        <v>1713158919</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6769,6 +7152,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6787,7 +7171,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710481882</v>
+        <v>1713159339</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6805,6 +7189,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6823,7 +7208,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710482679</v>
+        <v>1713159390</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6841,6 +7226,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6859,7 +7245,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710483227</v>
+        <v>1713159423</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6877,6 +7263,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6895,7 +7282,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710563331</v>
+        <v>1713159745</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6905,7 +7292,7 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6913,6 +7300,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6931,7 +7319,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710563754</v>
+        <v>1713237694</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6941,7 +7329,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6949,6 +7337,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6967,7 +7356,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710563858</v>
+        <v>1713238090</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6985,6 +7374,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7003,7 +7393,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710564452</v>
+        <v>1713239326</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7021,6 +7411,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7039,7 +7434,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710564805</v>
+        <v>1713239759</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7057,6 +7452,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7075,7 +7471,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710564825</v>
+        <v>1713240935</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7085,12 +7481,17 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7512,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710564943</v>
+        <v>1713241302</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7129,6 +7530,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7147,7 +7549,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710567098</v>
+        <v>1713241424</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7157,7 +7559,7 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7165,6 +7567,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7183,7 +7586,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710567462</v>
+        <v>1713241528</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7201,6 +7604,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7219,7 +7623,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710570414</v>
+        <v>1713241625</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7237,6 +7641,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7255,7 +7664,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710570998</v>
+        <v>1713242007</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7273,6 +7682,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7291,7 +7701,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710571156</v>
+        <v>1713242750</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7301,12 +7711,17 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7742,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710648811</v>
+        <v>1713243180</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7337,7 +7752,7 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -7345,6 +7760,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7363,7 +7779,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710649208</v>
+        <v>1713243286</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7381,6 +7797,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7399,7 +7816,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710651780</v>
+        <v>1713324057</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7417,6 +7834,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7435,7 +7857,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710652197</v>
+        <v>1713324295</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7453,6 +7875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7471,7 +7894,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710653684</v>
+        <v>1713326195</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7489,6 +7912,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7507,7 +7935,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710654216</v>
+        <v>1713326492</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7525,6 +7953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7543,7 +7972,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710654283</v>
+        <v>1713326706</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7561,6 +7990,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7579,7 +8013,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710654579</v>
+        <v>1713326945</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7597,6 +8031,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7615,7 +8050,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710654707</v>
+        <v>1713327521</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7625,12 +8060,17 @@
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -7651,7 +8091,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710654757</v>
+        <v>1713327898</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7669,6 +8109,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7687,7 +8128,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710656301</v>
+        <v>1713327951</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7697,7 +8138,7 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -7705,6 +8146,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7723,7 +8165,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710656749</v>
+        <v>1713328059</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -7733,12 +8175,17 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -7759,7 +8206,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710657126</v>
+        <v>1713328329</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7777,6 +8224,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7795,7 +8243,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710734048</v>
+        <v>1713328616</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7805,7 +8253,7 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -7813,6 +8261,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7831,7 +8280,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710734456</v>
+        <v>1713332671</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7841,7 +8290,7 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -7849,6 +8298,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7867,7 +8317,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710735852</v>
+        <v>1713333201</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7877,7 +8327,7 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -7885,6 +8335,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7903,7 +8354,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710736191</v>
+        <v>1713411065</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7913,12 +8364,17 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -7939,7 +8395,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710736584</v>
+        <v>1713411498</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7949,7 +8405,7 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7957,6 +8413,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7975,7 +8432,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710736936</v>
+        <v>1713411514</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7985,12 +8442,17 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8473,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710737726</v>
+        <v>1713411853</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8021,7 +8483,7 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -8029,6 +8491,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8047,7 +8510,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710738063</v>
+        <v>1713412013</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -8065,6 +8528,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8083,7 +8547,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710738331</v>
+        <v>1713412465</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -8101,6 +8565,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8119,7 +8588,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710738357</v>
+        <v>1713412855</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -8137,6 +8606,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8155,7 +8625,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710738572</v>
+        <v>1713413875</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -8165,12 +8635,17 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8666,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710738909</v>
+        <v>1713414291</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -8201,7 +8676,7 @@
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -8209,6 +8684,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8227,7 +8703,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710739310</v>
+        <v>1713414683</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -8245,6 +8721,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8263,7 +8740,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710740423</v>
+        <v>1713414759</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -8281,6 +8758,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8299,7 +8781,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710740854</v>
+        <v>1713415216</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -8317,6 +8799,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8335,7 +8818,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710741324</v>
+        <v>1713415397</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -8353,6 +8836,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8371,7 +8859,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710741762</v>
+        <v>1713415894</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -8389,6 +8877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8407,7 +8896,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710822081</v>
+        <v>1713499406</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -8425,6 +8914,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8443,7 +8933,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710822485</v>
+        <v>1713499686</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8461,6 +8951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8479,7 +8970,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710822953</v>
+        <v>1713499972</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8497,6 +8988,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8515,7 +9011,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710823366</v>
+        <v>1713500159</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8533,6 +9029,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8551,7 +9048,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710823663</v>
+        <v>1713500846</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8569,6 +9066,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8587,7 +9089,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710824030</v>
+        <v>1713501218</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -8605,6 +9107,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8623,7 +9126,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710826166</v>
+        <v>1713501246</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8641,6 +9144,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8659,7 +9163,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710826573</v>
+        <v>1713501536</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8677,6 +9181,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8695,7 +9200,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710826838</v>
+        <v>1713501720</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -8705,7 +9210,7 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -8713,6 +9218,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8731,7 +9237,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710827225</v>
+        <v>1713502414</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -8741,7 +9247,7 @@
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -8749,6 +9255,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8767,7 +9274,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710827331</v>
+        <v>1713502860</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -8777,7 +9284,7 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -8785,6 +9292,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8803,7 +9311,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710827494</v>
+        <v>1713504221</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -8813,12 +9321,17 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -8839,7 +9352,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710827626</v>
+        <v>1713504606</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -8857,6 +9370,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8875,7 +9389,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710827778</v>
+        <v>1713504774</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -8893,6 +9407,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8911,7 +9426,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711081589</v>
+        <v>1713755622</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8929,6 +9444,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8947,7 +9467,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711082030</v>
+        <v>1713755987</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8965,6 +9485,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8983,7 +9504,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711083177</v>
+        <v>1713756246</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -9001,6 +9522,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9019,7 +9545,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711083615</v>
+        <v>1713756582</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -9037,6 +9563,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9055,7 +9582,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711084073</v>
+        <v>1713758107</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -9073,6 +9600,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9091,7 +9619,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711084467</v>
+        <v>1713758444</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -9109,6 +9637,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9127,7 +9656,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711084747</v>
+        <v>1713758486</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -9137,7 +9666,7 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -9145,6 +9674,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9163,7 +9693,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711084787</v>
+        <v>1713759766</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -9173,7 +9703,7 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -9181,6 +9711,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9199,7 +9730,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711085248</v>
+        <v>1713760144</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -9217,6 +9748,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9235,7 +9767,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711086326</v>
+        <v>1713760315</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -9245,7 +9777,7 @@
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -9253,6 +9785,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9271,7 +9804,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711086859</v>
+        <v>1713762011</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -9281,12 +9814,17 @@
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9845,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711087101</v>
+        <v>1713762377</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -9325,6 +9863,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9343,7 +9882,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711088791</v>
+        <v>1713762673</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -9353,7 +9892,7 @@
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -9361,6 +9900,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9379,7 +9919,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711089347</v>
+        <v>1713846813</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -9389,12 +9929,17 @@
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9960,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711170156</v>
+        <v>1713847155</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -9425,7 +9970,7 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -9433,6 +9978,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9451,7 +9997,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711170610</v>
+        <v>1713848247</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -9461,12 +10007,17 @@
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9487,7 +10038,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711170776</v>
+        <v>1713848740</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -9505,6 +10056,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9523,7 +10075,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711170897</v>
+        <v>1713849310</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -9541,6 +10093,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9559,7 +10116,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711171299</v>
+        <v>1713849615</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -9577,6 +10134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9595,7 +10153,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711171595</v>
+        <v>1713849753</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -9605,7 +10163,7 @@
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -9613,6 +10171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9631,7 +10190,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711172062</v>
+        <v>1713849785</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -9641,12 +10200,17 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9667,7 +10231,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711172092</v>
+        <v>1713850125</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -9677,7 +10241,7 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -9685,6 +10249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9703,7 +10268,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711172410</v>
+        <v>1713850548</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -9713,12 +10278,17 @@
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9739,7 +10309,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711172667</v>
+        <v>1713850995</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -9757,6 +10327,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9775,7 +10346,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711173870</v>
+        <v>1713851136</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -9785,7 +10356,7 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -9793,6 +10364,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9811,7 +10383,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711174304</v>
+        <v>1713852211</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -9821,12 +10393,17 @@
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9847,7 +10424,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711174526</v>
+        <v>1713852712</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -9857,7 +10434,7 @@
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -9865,6 +10442,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9883,7 +10461,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711174979</v>
+        <v>1713932092</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -9893,12 +10471,17 @@
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9919,7 +10502,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711249864</v>
+        <v>1713932454</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -9929,7 +10512,7 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -9937,6 +10520,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9955,7 +10539,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1711250369</v>
+        <v>1713932818</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -9965,12 +10549,17 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -9991,7 +10580,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1711254668</v>
+        <v>1713933029</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -10001,7 +10590,7 @@
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -10009,6 +10598,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10027,7 +10617,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1711255059</v>
+        <v>1713933293</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -10045,6 +10635,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10063,7 +10654,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1711255473</v>
+        <v>1713933383</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -10081,6 +10672,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10099,7 +10691,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1711255815</v>
+        <v>1713933733</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -10117,6 +10709,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10135,7 +10728,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1711255925</v>
+        <v>1713935121</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -10145,7 +10738,7 @@
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -10153,6 +10746,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10171,7 +10765,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1711258854</v>
+        <v>1713935565</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -10181,7 +10775,7 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -10189,6 +10783,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10207,7 +10802,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1711259364</v>
+        <v>1713936589</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -10217,7 +10812,7 @@
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -10225,6 +10820,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10243,7 +10839,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1711259466</v>
+        <v>1713937042</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -10253,7 +10849,7 @@
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -10261,6 +10857,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10279,7 +10876,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1711259839</v>
+        <v>1713937778</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -10289,7 +10886,7 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -10297,6 +10894,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10315,7 +10913,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1711259896</v>
+        <v>1713938242</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -10333,6 +10931,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10351,7 +10950,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1711260786</v>
+        <v>1713938676</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -10361,7 +10960,7 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -10369,6 +10968,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10387,7 +10987,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1711261202</v>
+        <v>1714011463</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -10397,12 +10997,17 @@
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -10423,7 +11028,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1711261413</v>
+        <v>1714011849</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -10441,6 +11046,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10459,7 +11065,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1711337465</v>
+        <v>1714016902</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -10477,6 +11083,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10495,7 +11102,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1711337869</v>
+        <v>1714017219</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -10513,6 +11120,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10531,7 +11139,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1711341168</v>
+        <v>1714017270</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -10541,7 +11149,7 @@
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -10549,6 +11157,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10567,7 +11176,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1711341592</v>
+        <v>1714017291</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -10585,6 +11194,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10603,7 +11213,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1711342310</v>
+        <v>1714017403</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -10621,6 +11231,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10639,7 +11254,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1711342608</v>
+        <v>1714017721</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -10657,6 +11272,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10675,7 +11291,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1711342857</v>
+        <v>1714017962</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -10693,6 +11309,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10711,7 +11332,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1711342933</v>
+        <v>1714018413</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -10729,6 +11350,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10747,7 +11369,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1711343173</v>
+        <v>1714019161</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -10757,12 +11379,17 @@
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
           <t>physical</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>
@@ -10783,7 +11410,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1711343766</v>
+        <v>1714019611</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -10793,7 +11420,7 @@
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -10801,6 +11428,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10819,7 +11447,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1711344219</v>
+        <v>1714020094</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -10837,6 +11465,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10855,7 +11484,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1711345105</v>
+        <v>1714020234</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -10873,6 +11502,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10891,7 +11525,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1711345634</v>
+        <v>1714020725</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -10909,6 +11543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10927,7 +11562,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1711345794</v>
+        <v>1714102572</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -10945,6 +11580,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10963,7 +11603,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1711346271</v>
+        <v>1714102842</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -10981,6 +11621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10999,7 +11640,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1711425779</v>
+        <v>1714103040</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -11009,7 +11650,7 @@
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -11017,6 +11658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11035,7 +11677,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1711426146</v>
+        <v>1714103118</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -11053,6 +11695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11071,7 +11714,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1711428412</v>
+        <v>1714103518</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -11089,6 +11732,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11107,7 +11755,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1711428762</v>
+        <v>1714103825</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -11125,6 +11773,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11143,7 +11792,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1711429418</v>
+        <v>1714103879</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -11161,6 +11810,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11179,7 +11833,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1711429876</v>
+        <v>1714103932</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -11197,6 +11851,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11215,7 +11870,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1711429983</v>
+        <v>1714104203</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -11233,6 +11888,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11251,7 +11907,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1711430017</v>
+        <v>1714105820</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -11261,7 +11917,7 @@
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -11269,6 +11925,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11287,7 +11944,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1711430091</v>
+        <v>1714106337</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -11297,7 +11954,7 @@
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -11305,6 +11962,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11323,7 +11981,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1711430399</v>
+        <v>1714107940</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -11333,7 +11991,7 @@
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
+          <t>TeaRoom.WaterDispenser001.state: on</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -11341,6 +11999,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11359,7 +12018,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1711430865</v>
+        <v>1714108465</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -11369,7 +12028,7 @@
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
+          <t>TeaRoom.WaterDispenser001.state: off</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -11377,186 +12036,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>WaterDispenser_Operation</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
-        <v>1711431322</v>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>WaterDispenser_Operation</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>1711433024</v>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>WaterDispenser_Operation</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>1711433504</v>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>WaterDispenser_Operation</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D308" t="n">
-        <v>1711435428</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>TeaRoom.WaterDispenser001.state: on</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>WaterDispenser_Operation</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D309" t="n">
-        <v>1711436046</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>TeaRoom.WaterDispenser001.state: off</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I304" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
